--- a/user_mig/NOVA_테스트결과_20260808.xlsx
+++ b/user_mig/NOVA_테스트결과_20260808.xlsx
@@ -71,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -83,6 +83,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -454,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3970,7 +3973,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>📍 클릭 → 목록 맨 위 고정</t>
+          <t>📍 클릭 → 목록 맨 위 고정, 새로고침 후 유지</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3978,16 +3981,12 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>브라우저가 페이지를 못 열어 보류(정적: pinned 정렬 코드 존재)</t>
-        </is>
-      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4010,7 +4009,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>✎ 클릭 → 제목 변경·유지</t>
+          <t>✎ → 제목 변경·유지</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4018,16 +4017,12 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>정적: rename/PATCH title 코드 존재</t>
-        </is>
-      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4050,7 +4045,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>메시지 전송 → 상단 이동</t>
+          <t>메시지 전송 → 핀 아래·나머지 위로 이동</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4058,16 +4053,12 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>정적: last_modified 정렬 코드 존재</t>
-        </is>
-      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4090,7 +4081,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>스니펫 강조·클릭 이동</t>
+          <t>스니펫 표시 + 클릭 이동</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4098,16 +4089,12 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>정적: /sessions/search + snippet 코드 존재. API 는 T1-3 PASS</t>
-        </is>
-      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4125,12 +4112,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>폴더 그룹</t>
+          <t>폴더 드래그·다중선택</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>폴더별 접이식 그룹·개수</t>
+          <t>폴더로 끌어 놓기 / Ctrl·Shift 다중선택 후 일괄 이동</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4140,12 +4127,12 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>미실행</t>
+          <t>구현완료</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>정적: folder 코드 55곳. API 는 T2-3 PASS</t>
+          <t>★1차 FAIL 은 고장이 아니라 미구현(draggable·ctrlKey 부재). 커밋 81c4ca2 로 신규 구현 — 재확인 필요</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4157,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>LAN http 에서 복사 동작</t>
+          <t>LAN http 에서 복사 → 실제 붙여넣기 성공</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4178,14 +4165,14 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>★정적: clipboard + execCommand 폴백 코드 존재 — 실제 동작은 눈확인 필요</t>
+          <t>★가장 우려한 함정 — execCommand 폴백 정상 동작</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4197,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>▶미리보기 → 샌드박스 iframe</t>
+          <t>▶미리보기 → 샌드박스 iframe 렌더</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4218,16 +4205,12 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>정적: sandbox 속성 지정 코드 존재</t>
-        </is>
-      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4250,7 +4233,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>생성 중 실시간 렌더·완료 후 안정</t>
+          <t>생성 중 마크다운 실시간 정리</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4258,16 +4241,12 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>정적: /chat/stream + 15종 이벤트 핸들러 존재. 서버 스트림은 T2-2s PASS</t>
-        </is>
-      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4290,7 +4269,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>다운로드 버튼·썸네일</t>
+          <t>썸네일 + 다운로드 버튼</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4298,16 +4277,12 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>정적: authFetchBlob 경로 존재. 서버측 downloads 는 TA-2 PASS</t>
-        </is>
-      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4330,7 +4305,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>md 다운로드 내용·인코딩</t>
+          <t>md 내용·UTF-8 인코딩</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4338,16 +4313,12 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>서버측 T1-4 PASS</t>
-        </is>
-      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4370,7 +4341,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>F5 후 그림·링크·핀·폴더·제목 유지</t>
+          <t>이미지·다운로드·핀·폴더·제목 유지 + **배치 순서**</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4380,12 +4351,12 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>미실행</t>
+          <t>수정완료</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>★영속성 핵심 — 눈확인 필요</t>
+          <t>★파일은 남았으나 생성물이 마지막 줄에 뭉쳤다. 원인=turn 매칭(turn 이 항상 1). 시각 기준으로 교체(커밋 fd6b8bb), 실서버 재현 스크립트로 전후 확인</t>
         </is>
       </c>
     </row>
@@ -4418,16 +4389,12 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>서버측 T2-2/T2-2b PASS</t>
-        </is>
-      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4450,7 +4417,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>'/' 입력 → 템플릿 팝업</t>
+          <t>'/' 입력 → 템플릿 팝업·삽입</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4458,7 +4425,7 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G106" s="5" t="inlineStr">
+      <c r="G106" s="6" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
@@ -4490,7 +4457,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>↻ → 새 답변 대체</t>
+          <t>↻ → 새 답변이 이전 답변 대체</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4498,16 +4465,12 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>서버측 TA-3 PASS</t>
-        </is>
-      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4538,14 +4501,14 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G108" s="5" t="inlineStr">
+      <c r="G108" s="6" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>서버측 T3-1/T3-1b PASS</t>
+          <t>서버측 T3-1·T3-1b PASS</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4541,7 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G109" s="5" t="inlineStr">
+      <c r="G109" s="6" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
@@ -4610,7 +4573,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>업로드 이미지 구도 반영</t>
+          <t>업로드 이미지 구도·색감 반영</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4618,14 +4581,94 @@
           <t>수동[M]</t>
         </is>
       </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>미실행</t>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>IP-Adapter 미적용 한계(문서화됨)</t>
+          <t>"그림은 잘 그렸어" — 합격 기준(구도·색감) 충족. 얼굴 동일성은 IP-Adapter 미적용 한계</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>신규기능</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>클립보드 이미지 붙여넣기</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>다른 곳에서 복사한 이미지를 Ctrl+V 로 첨부</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>수동[M]</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>구현완료</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>사용자 요청. 커밋 b687b62 — 재확인 필요. 텍스트 붙여넣기는 기본 동작 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>신규기능</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>첨부 이미지 썸네일</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>첨부 칩에 28px 미리보기</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>수동[M]</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>구현완료</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>사용자 요청. 커밋 b687b62 — 재확인 필요</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4648,12 +4691,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>값</t>
         </is>
@@ -4679,7 +4722,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>192.168.21.112:8600 (nexus-web:clienttools-20260808)</t>
+          <t>192.168.21.112:8600 (nexus-web:folderdnd-20260808)</t>
         </is>
       </c>
     </row>
@@ -4730,90 +4773,92 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>수동(UI) 미실행</t>
+          <t>수동(UI) 총계</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PASS</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>★ 제품 결함</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>E6 프롬프트 인젝션 — 발견 후 수정·배포 완료(커밋 70fb9e2)</t>
-        </is>
+          <t xml:space="preserve">  수정·구현 완료(재확인 대기)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   최초 관측</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>3/3 순응 — JAILBROKEN / OVERRIDE_OK / YES_MASTER</t>
-        </is>
+          <t xml:space="preserve">  미실행</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   수정</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>core/verification/injection_guard.py + Tier 1 submit_message 배선</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   검증</t>
+          <t>★ 제품 결함</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>실서버 36/36 — 공격 8x3경로 차단, 정상 12종 통과. 단위 22건</t>
+          <t>E6 프롬프트 인젝션 — 발견 후 수정·배포 완료(커밋 70fb9e2)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   최초 관측</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>3/3 순응 — JAILBROKEN / OVERRIDE_OK / YES_MASTER</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WARN 2건</t>
+          <t xml:space="preserve">   수정</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TA-17 형식 지시(3줄) / NUM-2 곱셈 — 둘 다 A.X-4.0 능력 한계</t>
+          <t>core/verification/injection_guard.py + Tier 1 submit_message 배선</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WARN 1건</t>
+          <t xml:space="preserve">   검증</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>TA-5b 임의 토큰 재현 1회 실패 — 서버가 URL 을 확정하는 설계의 근거</t>
+          <t>실서버 36/36 — 공격 8x3경로 차단, 정상 12종 통과. 단위 22건</t>
         </is>
       </c>
     </row>
@@ -4824,112 +4869,176 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>검사 결함으로 정정된 1차 FAIL</t>
+          <t>WARN 2건</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10건</t>
+          <t>TA-17 형식 지시(3줄) / NUM-2 곱셈 — 둘 다 A.X-4.0 능력 한계</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  형식 오류</t>
+          <t>WARN 1건</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>instructions→text, name/body→title/text, 단건→목록, format→fmt</t>
+          <t>TA-5b 임의 토큰 재현 1회 실패 — 서버가 URL 을 확정하는 설계의 근거</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  판정 오류</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>링크를 모델 텍스트에서 찾음(실제는 downloads 필드)</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  대상 오류</t>
+          <t>검사 결함으로 정정된 1차 FAIL</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>IDOR 를 업로드로 검사(/v1/download 는 생성물 전용)</t>
+          <t>10건</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  풀 오류</t>
+          <t xml:space="preserve">  형식 오류</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CLI 도구를 도달 불가한 TIER_S 풀(7개)에서 잼</t>
+          <t>instructions→text, name/body→title/text, 단건→목록, format→fmt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  반환형 오류</t>
+          <t xml:space="preserve">  판정 오류</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>build_answer_warnings 를 리스트로 오인(실제 str)</t>
+          <t>링크를 모델 텍스트에서 찾음(실제는 downloads 필드)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  인코딩 오류</t>
+          <t xml:space="preserve">  대상 오류</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>head -c 가 한글을 잘라 UnicodeDecodeError</t>
+          <t>IDOR 를 업로드로 검사(/v1/download 는 생성물 전용)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  풀 오류</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CLI 도구를 도달 불가한 TIER_S 풀(7개)에서 잼</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UI 미실행 사유</t>
+          <t xml:space="preserve">  반환형 오류</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Chrome 이 http://192.168.21.112:8600 을 chrome-error 로 표시(curl 은 200)</t>
+          <t>build_answer_warnings 를 리스트로 오인(실제 str)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UI 정적 확인</t>
+          <t xml:space="preserve">  인코딩 오류</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>A1~D5 해당 코드 경로는 index.html 에 존재 — 눈검증만 남음</t>
+          <t>head -c 가 한글을 잘라 UnicodeDecodeError</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>UI 눈검증</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>사용자 수행 완료 — 체크리스트 user_mig/TEST_사용자수동_20260808.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  발견 결함</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>C2 새로고침 후 생성물 배치 오류 → 수정·배포(fd6b8bb)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  발견 미구현</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>A5 폴더 드래그·다중선택 → 신규 구현·배포(81c4ca2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  신규 기능</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>F1 클립보드 이미지 붙여넣기 / F2 첨부 썸네일 → 구현·배포(b687b62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  남은 미실행</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>D2 프롬프트 팝업 / D4 편집·분기 / D5 프로젝트 (서버측은 모두 PASS)</t>
         </is>
       </c>
     </row>
